--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7655,6 +7655,132 @@
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>113487960</v>
+      </c>
+      <c r="B60" t="n">
+        <v>74307</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>308</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Klen al, Vg</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>339419</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6431398</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-12-02</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-12-02</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Vid skada på al vid liten bäck i skogen, nära en stig. Högt upp på stammen.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Robin Karlsson, Sebastian Kirppu, Lars Gerre, Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -7660,7 +7660,7 @@
         <v>113487960</v>
       </c>
       <c r="B60" t="n">
-        <v>74307</v>
+        <v>74329</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -7660,7 +7660,7 @@
         <v>113487960</v>
       </c>
       <c r="B60" t="n">
-        <v>74329</v>
+        <v>74332</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -7660,7 +7660,7 @@
         <v>113487960</v>
       </c>
       <c r="B60" t="n">
-        <v>74332</v>
+        <v>74338</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -7660,7 +7660,7 @@
         <v>113487960</v>
       </c>
       <c r="B60" t="n">
-        <v>74338</v>
+        <v>74345</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -7660,7 +7660,7 @@
         <v>113487960</v>
       </c>
       <c r="B60" t="n">
-        <v>74345</v>
+        <v>74347</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -7660,7 +7660,7 @@
         <v>113487960</v>
       </c>
       <c r="B60" t="n">
-        <v>74347</v>
+        <v>74375</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -7786,7 +7786,7 @@
         <v>117443200</v>
       </c>
       <c r="B61" t="n">
-        <v>57534</v>
+        <v>57535</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -8504,7 +8504,7 @@
         <v>120845281</v>
       </c>
       <c r="B67" t="n">
-        <v>97245</v>
+        <v>97255</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>121352669</v>
       </c>
       <c r="B68" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -8625,7 +8625,7 @@
         <v>121352669</v>
       </c>
       <c r="B68" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -8625,7 +8625,7 @@
         <v>121352669</v>
       </c>
       <c r="B68" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -8625,7 +8625,7 @@
         <v>121352669</v>
       </c>
       <c r="B68" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8864,6 +8864,122 @@
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126142550</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kvarnen, Vg</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>339291</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6431458</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -8869,7 +8869,7 @@
         <v>126142550</v>
       </c>
       <c r="B70" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8980,6 +8980,225 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126273797</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Ryksbäcken, Ryksbäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>339443</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6431497</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126273837</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Ryksbäcken, Ryksbäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>339455</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6431504</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ett tjugotal plantor</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9199,6 +9199,113 @@
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126290429</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Ryksbäcken, Ryksbäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>339375</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6431378</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8869,7 +8869,7 @@
         <v>126142550</v>
       </c>
       <c r="B70" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>126273797</v>
       </c>
       <c r="B71" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>126273837</v>
       </c>
       <c r="B72" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>126290429</v>
       </c>
       <c r="B73" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9305,6 +9305,118 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126348877</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57653</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Röda berget, Vg</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>339364</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6431202</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Födosök av spillkråka</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -8985,7 +8985,7 @@
         <v>126273797</v>
       </c>
       <c r="B71" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>126273837</v>
       </c>
       <c r="B72" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -8869,7 +8869,7 @@
         <v>126142550</v>
       </c>
       <c r="B70" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>126273797</v>
       </c>
       <c r="B71" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>126273837</v>
       </c>
       <c r="B72" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>126290429</v>
       </c>
       <c r="B73" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>126348877</v>
       </c>
       <c r="B74" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9418,6 +9418,126 @@
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>130304053</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kvarnen, Vg</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>339380</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6431466</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Spår av födosök i träd.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -9069,7 +9069,7 @@
         <v>0</v>
       </c>
       <c r="AE71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG71" t="b">
         <v>0</v>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -9423,7 +9423,7 @@
         <v>130304053</v>
       </c>
       <c r="B75" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -9423,7 +9423,7 @@
         <v>130304053</v>
       </c>
       <c r="B75" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -9423,7 +9423,7 @@
         <v>130304053</v>
       </c>
       <c r="B75" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -9423,7 +9423,7 @@
         <v>130304053</v>
       </c>
       <c r="B75" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 12138-2021 artfynd.xlsx
+++ b/artfynd/A 12138-2021 artfynd.xlsx
@@ -9423,7 +9423,7 @@
         <v>130304053</v>
       </c>
       <c r="B75" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
